--- a/DATA/MODELADO/Tensores/Exp04/metadata_tensor.xlsx
+++ b/DATA/MODELADO/Tensores/Exp04/metadata_tensor.xlsx
@@ -550,7 +550,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-31 01:15</t>
+          <t>2026-07-31 02:23</t>
         </is>
       </c>
     </row>
